--- a/docs/comp190-schedule.xlsx
+++ b/docs/comp190-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\comp190-web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BBF1E9-F90E-4823-B049-3B9C2791D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C834FDB-5465-4CE2-964A-89B8A8B72552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Required reading</t>
-  </si>
-  <si>
-    <t>AI and Intellectual Property</t>
   </si>
   <si>
     <t>wrapup</t>
@@ -1011,7 +1008,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="7"/>
@@ -1040,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="12"/>
     </row>
@@ -1092,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" s="12"/>
     </row>
@@ -1101,7 +1098,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9">
         <v>46294</v>
@@ -1109,7 +1106,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="26"/>
       <c r="F6" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31"/>
@@ -1163,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I8" s="12"/>
     </row>
@@ -1220,14 +1217,12 @@
         <v>8</v>
       </c>
       <c r="E11" s="23"/>
-      <c r="F11" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="F11" s="11"/>
       <c r="G11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" s="13"/>
     </row>
@@ -1236,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="9">
         <v>46322</v>
@@ -1244,7 +1239,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="24"/>
       <c r="F12" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31"/>
@@ -1277,7 +1272,7 @@
     <row r="14" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35"/>
       <c r="B14" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="9">
         <v>46324</v>
@@ -1285,7 +1280,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="23"/>
       <c r="F14" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14" s="20"/>
       <c r="H14" s="21"/>
@@ -1313,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I15" s="12"/>
     </row>
@@ -1348,7 +1343,7 @@
       <c r="D17" s="10"/>
       <c r="E17" s="23"/>
       <c r="F17" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="21"/>
@@ -1376,7 +1371,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18" s="12"/>
     </row>
@@ -1411,7 +1406,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>12</v>
@@ -1435,13 +1430,13 @@
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I21" s="13"/>
     </row>
@@ -1463,7 +1458,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
